--- a/산출물/99_제출파일/프로그램_목록.xlsx
+++ b/산출물/99_제출파일/프로그램_목록.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프로그램 목록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'프로그램 목록'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,14 +40,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
       <color rgb="FF4E5968"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="FF191F28"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -55,13 +52,25 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="FF191F28"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="FF4E5968"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="FF8B95A1"/>
-      <sz val="8.5"/>
+      <color rgb="FF191F28"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FF191F28"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF6B7684"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -108,31 +117,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -500,584 +512,1298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>프로그램 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>프로그램 목록  ·  하모니</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니(harmony) · 미니앱(apps/miniapp) + 백엔드(apps/api) · 담당 이상혁·김민혁 · 2026-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>실제 소스 코드 기준 프로그램·모듈 목록이다.</t>
-        </is>
-      </c>
+          <t>하모니 미니앱(apps/miniapp)·서버 API(apps/api) · 작성 양록빈(QA) · 실제 소스 기준 · 2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>프로그램 목록 (실제 소스 기준 · 구분별 집계: 화면 7 · API 10 · 공통 모듈 10 · 컴포넌트 6 · 합계 33)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>미니앱 — 화면 · 진입</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>프로그램 ID</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>프로그램명</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>프로그램 설명</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>관련 테이블</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>파일·경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>파일</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
+          <t>▸ 화면 (apps/miniapp 라우트)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>src/main.tsx</t>
-        </is>
+      <c r="A7" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>진입점. theme.css import(WebView 밖에서는 차단)</t>
+          <t>PG-SCR-000</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>공통 셸·라우터</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>화면 전환(홈/스튜디오/설정/커뮤니티)과 온보딩 게이트, 개발자 모드 상태 관리</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>src/App.tsx</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>src/App.tsx</t>
-        </is>
+      <c r="A8" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>라우터(홈·스튜디오·설정·커뮤니티) + 온보딩 게이트 + 개발자 모드 상태</t>
+          <t>PG-SCR-001</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>스플래시</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>구동 시 라이트 브랜드 리빌(스플래시 게이트)</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/Splash.tsx</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>src/theme.css</t>
-        </is>
+      <c r="A9" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>라이트 테마 토큰(자체 토스풍, 100% 라이트)</t>
+          <t>PG-SCR-002</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>온보딩</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>닉네임 입력 후 토스 익명키 발급. 가입·로그인 아님</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/Onboarding.tsx</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>src/routes/Splash.tsx</t>
-        </is>
+      <c r="A10" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>구동 시 짧은 라이트 브랜드 화면(스플래시 게이트)</t>
+          <t>PG-SCR-003</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>홈</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>인사 화면과 최근 곡 이어하기 목록</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>sessions(로컬)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/Home.tsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>src/routes/Onboarding.tsx</t>
-        </is>
+      <c r="A11" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>닉네임 입력 + getAnonymousKey(가입·로그인 아님)</t>
+          <t>PG-SCR-004</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>스튜디오</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>악기·스타일 선택, 코드/멜로디/드럼/제스처 연주, 녹음·합주·음 편집, 레이어 추가·삭제, 재생바</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>sessions, tracks</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/Studio.tsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>src/routes/Home.tsx</t>
-        </is>
+      <c r="A12" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>인사 + 최근 곡 목록(이어하기)</t>
+          <t>PG-SCR-005</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>커뮤니티</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>공개곡 보드, 들어보기, 좋아요, 댓글·신고, 가져오기·합주 올리기</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>sessions, tracks, comments, reactions</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/Community.tsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>src/routes/Studio.tsx</t>
-        </is>
+      <c r="A13" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>풀스튜디오 셸: 악기·스타일, 28코드, 멜로디, 드럼, 제스처, 효과음, 기타·베이스 프렛보드, 녹음, 합주, 음 편집, 전체화면, 레이어 추가·삭제, 재생바(스크럽·재생·일시정지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>src/routes/Community.tsx</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>음원 게시판: 아바타·음원명·길이, 들어보기, 좋아요, 다중 선택 가져오기(로컬 합본 레이어)</t>
-        </is>
-      </c>
+          <t>PG-SCR-006</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>이모지 프로필·닉네임, 개발자 모드, 버전, 법적 고지</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/Settings.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>▸ 서버 API (apps/api/server.mjs · node:http+node:sqlite)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>src/routes/Settings.tsx</t>
-        </is>
+      <c r="A15" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>이모지 프로필·닉네임·버전·개발자 모드 토글·법적 고지</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>미니앱 — 스튜디오 컴포넌트 (src/components/studio)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>파일</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>역할</t>
+          <t>PG-API-001</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>헬스 체크</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>GET /healthz 서버 상태 확인</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>PG-API-002</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>커뮤니티 목록</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>GET /community 공개곡 목록(최신·인기), 좋아요·댓글 수 포함</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>sessions, reactions, comments</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PG-API-003</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>세션 생성·발행</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>POST /sessions 트랙 업로드, 6자리 코드 발급, 커뮤니티 공개 발행(콘텐츠 중복 방지)</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>sessions, tracks</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>PG-API-004</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>세션 조회</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>GET /sessions/:code 코드로 세션·트랙 로드</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>sessions, tracks</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>chords.ts</t>
-        </is>
+      <c r="A19" s="7" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>UI·음악 상수: 28코드·로마숫자·색·악기·스타일·건반·기타베이스 튜닝·드럼 8피스·2D 드럼킷 배치</t>
+          <t>PG-API-005</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>트랙 얹기</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>POST /sessions/:code/tracks 세션에 내 레이어 추가(비동기 합주)</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>tracks, sessions</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>ChordMatrix.tsx</t>
-        </is>
+      <c r="A20" s="7" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>28코드 매트릭스(7×4, 최대 6개) + 빠른 프리셋</t>
+          <t>PG-API-006</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>댓글 조회</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>GET /sessions/:code/comments 숨김 제외 최신순</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>InstrumentCombo.tsx</t>
-        </is>
+      <c r="A21" s="7" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>악기·스타일 연동 바텀시트 콤보(화면 동일·소리만 변경)</t>
+          <t>PG-API-007</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>댓글 작성</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>POST /sessions/:code/comments 동일 내용 60초 중복 방지</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>NotePadGrid.tsx</t>
-        </is>
+      <c r="A22" s="7" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>기타·베이스 크로매틱 계이름 패드(일반 6프렛·전체화면 13프렛)</t>
+          <t>PG-API-008</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>댓글 신고</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>POST /sessions/:code/comments/:id/report 서로 다른 신고자 누적 시 자동 숨김</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>comment_reports, comments</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>DrumPad.tsx</t>
-        </is>
+      <c r="A23" s="7" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
+          <t>PG-API-009</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>좋아요 토글</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>POST /sessions/:code/like 1인 1좋아요(토글)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>reactions, sessions</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PG-API-010</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>게시물 숨김</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>POST /sessions/:code/hide 운영용 숨김 처리</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>apps/api/server.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>▸ 공통 모듈 (핵심 로직)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-001</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>오디오 엔진</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>28코드·멜로디·드럼 발음, 실제 샘플과 합성 폴백, 샘플 정확 스케줄(저지연)</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>src/audio/engine.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-002</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>코드 리듀서</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>tick 이벤트 상태 전이(중복 금지·전환·터치 우선·폴리포니·드럼). 순수 함수, 단위테스트</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>src/audio/chordReducer.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-003</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>이벤트 계약</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>NoteEvent 정규화(코드·멜로디·드럼 통합), 하위호환 복원</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>tracks(events)</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>src/audio/events.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-004</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>트랜스포트</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>BPM·박자·메트로놈, tick과 ms 변환</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>src/audio/transport.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-005</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>제스처 인식</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>MediaPipe 손·얼굴 추적, 카메라 실패 시 터치로 폴백</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>src/audio/gesture.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-006</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>음정 변환</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>평균율 A4=440 음정 단일 기준. 순수 함수, 단위테스트</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>src/audio/tuning.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-007</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>음 편집 로직</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>이벤트와 편집 노트 변환·퀀타이즈. 순수 함수, 단위테스트</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/noteEdit.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-008</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>합주 클라이언트</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>세션 생성·조회·얹기·동기화, 클립보드, 프리로드 폴백</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>sessions, tracks</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/share.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-009</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>로컬 저장</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>솔로 곡 저장·목록·삭제(localStorage)</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/storage.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>PG-MOD-010</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>모듈</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>익명 식별</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>토스 익명키 2트랙(실호출·브라우저 폴백), 닉네임·이모지 프로필</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/identity.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>▸ 화면 컴포넌트 (스튜디오)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>PG-CMP-001</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>컴포넌트</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>코드 매트릭스</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>28코드 7×4 패드(최대 6선택)와 빠른 프리셋</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>src/components/studio/ChordMatrix.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>PG-CMP-002</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>컴포넌트</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>악기·스타일 콤보</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>악기·음색 바텀시트(화면 동일, 소리만 변경)</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>src/components/studio/InstrumentCombo.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>PG-CMP-003</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>컴포넌트</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>계이름 패드</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>기타·베이스 크로매틱 계이름 패드</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>src/components/studio/NotePadGrid.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>PG-CMP-004</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>컴포넌트</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>드럼 패드</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
           <t>드럼 8패드(타격 색 표시)</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>NoteEditor.tsx</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>음 편집 피아노롤(드래그 이동·길이·조옮김·퀀타이즈·미리듣기·재생 플레이헤드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>GestureFretboard.tsx</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>기타·베이스 제스처 오버레이(투명 실루엣 + 프렛 칸 + 활성 시 현 진동)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>DevOverlay.tsx</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>개발자 HUD(FPS·핑·네트워크)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>미니앱 — 도메인 로직</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>파일</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/engine.ts</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>오디오 엔진: setVoice, 28코드 buildChord(통일 옥타브), downChord·downNote, triggerHit, createVoice, audioNow. 실제 샘플 + 합성 폴백, 드럼킷, 음량. 저지연 스케줄링</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/events.ts</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>이벤트 계약: NoteEvent(코드·멜로디·드럼) + normalizeEvents(하위호환)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/chordReducer.ts</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>순수 reducer: tick 이벤트 처리(중복 방지·전환·터치 우선·폴리포니·드럼 hit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/transport.ts</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Tone.Transport 클럭: BPM·박자·메트로놈·tick↔ms 변환</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/gesture.ts</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>MediaPipe HandLandmarker(양손·존·2D 키트·손바닥/손가락) + 얼굴 중심(헤드뱅잉)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/gestureFx.ts</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>제스처 효과음: 손 흔들기→탬버린, 박수→박수, 헤드뱅잉→효과음</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>src/audio/tuning.ts</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>평균율 A4=440 음정 단일 진실원</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/notes.ts</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>음 이동(transpose)·한글 계이름(지판·에디터용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/noteEdit.ts</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>음 편집 핵심: 이벤트↔편집노트 변환·퀀타이즈(순수 함수, 단위테스트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/settings.ts</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>개발자 모드·제스처 효과음 on/off 플래그(localStorage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/identity.ts</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>getAnonymousKey(토스 실호출/브라우저 폴백 2트랙)·닉네임·이모지 프로필 저장</t>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>src/components/studio/DrumPad.tsx</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/storage.ts</t>
-        </is>
+      <c r="A41" s="7" t="n">
+        <v>32</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>로컬 곡 저장·목록·삭제(localStorage)</t>
+          <t>PG-CMP-005</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>컴포넌트</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>음 편집기</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>피아노롤(드래그 이동·길이·조옮김·퀀타이즈·미리듣기)</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>src/components/studio/NoteEditor.tsx</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/likes.ts</t>
-        </is>
+      <c r="A42" s="7" t="n">
+        <v>33</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>커뮤니티 좋아요(토글)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>src/lib/share.ts</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>합주 백엔드 클라이언트(생성·조회·얹기)·클립보드·핑·프리로드 폴백</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>백엔드 (apps/api)</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>파일</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>server.mjs</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>node:http + node:sqlite 무의존 API. GET /healthz, POST /sessions, GET /sessions/:code, POST /sessions/:code/tracks, 댓글·신고·좋아요</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>deploy/*</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>systemd(harmony-api.service)·nginx·certbot·deploy.sh(배포 스크립트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>설정 · 빌드</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>파일</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>apps/miniapp/granite.config.ts</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>앱인토스 앱 설정(appName·brand·카메라 권한)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>apps/miniapp/vite.config.ts</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Vite + React(단일화로 중복 방지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>apps/miniapp/.env</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>VITE_API_BASE(백엔드 URL, 형상관리 제외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>단위테스트(vitest) 7파일 58케이스: chordReducer · chordReducer.poly · tuning · events · loop · notes · noteEdit. 2026-06-25 재실행 58/58 통과(종료코드 0).</t>
+          <t>PG-CMP-006</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>컴포넌트</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>제스처 프렛보드</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>기타·베이스 제스처 오버레이(실루엣·프렛 칸·현 진동)</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>src/components/studio/GestureFretboard.tsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A50:B50"/>
+  <mergeCells count="7">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
